--- a/data_dictionary.xlsx
+++ b/data_dictionary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\OneDrive\Desktop\Eugene\KEMRI_Proj\KEMRI_P1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3936E469-DA02-4D4D-AE3B-D7D1452478B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FC0F6FC-D70E-4CB3-B9FB-7168D00E2DC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -590,7 +590,7 @@
     <col min="1" max="1" width="25" customWidth="1"/>
     <col min="2" max="2" width="50" customWidth="1"/>
     <col min="3" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="60" customWidth="1"/>
+    <col min="5" max="5" width="76.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
